--- a/Final_Speech_Evaluation.xlsx
+++ b/Final_Speech_Evaluation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brann\OneDrive\Desktop\CS614_GroupProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0935827-E627-4784-8F13-804E7349F75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3234FA1F-43E0-49FE-B7BD-01DE9A05CF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{7E1DB2E1-ADCC-46F1-9F0F-E353445E078F}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{7E1DB2E1-ADCC-46F1-9F0F-E353445E078F}"/>
   </bookViews>
   <sheets>
     <sheet name="Prompt 1" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -183,7 +183,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -523,6 +523,7 @@
   <dimension ref="A1:O38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5.5703125" bestFit="1" customWidth="1"/>
@@ -672,27 +673,27 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E5" s="3">
-        <f>AVERAGE(E2:E4)</f>
+        <f t="shared" ref="E5:J5" si="0">AVERAGE(E2:E4)</f>
         <v>3.6666666666666665</v>
       </c>
       <c r="F5" s="3">
-        <f>AVERAGE(F2:F4)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="G5" s="3">
-        <f>AVERAGE(G2:G4)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="H5" s="3">
-        <f>AVERAGE(H2:H4)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="I5" s="3">
-        <f>AVERAGE(I2:I4)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="J5" s="3">
-        <f>AVERAGE(J2:J4)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="K5" s="3">
@@ -808,27 +809,27 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E10" s="3">
-        <f>AVERAGE(E7:E9)</f>
+        <f t="shared" ref="E10:J10" si="1">AVERAGE(E7:E9)</f>
         <v>4.333333333333333</v>
       </c>
       <c r="F10" s="3">
-        <f>AVERAGE(F7:F9)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="G10" s="3">
-        <f>AVERAGE(G7:G9)</f>
+        <f t="shared" si="1"/>
         <v>4.666666666666667</v>
       </c>
       <c r="H10" s="3">
-        <f>AVERAGE(H7:H9)</f>
+        <f t="shared" si="1"/>
         <v>4.666666666666667</v>
       </c>
       <c r="I10" s="3">
-        <f>AVERAGE(I7:I9)</f>
+        <f t="shared" si="1"/>
         <v>3.3333333333333335</v>
       </c>
       <c r="J10" s="3">
-        <f>AVERAGE(J7:J9)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K10" s="3">
@@ -994,31 +995,31 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E18" s="3">
-        <f>AVERAGE(E15:E17)</f>
-        <v>3</v>
-      </c>
-      <c r="F18" s="3">
-        <f>AVERAGE(F15:F17)</f>
-        <v>3</v>
-      </c>
-      <c r="G18" s="3">
-        <f>AVERAGE(G15:G17)</f>
-        <v>3</v>
-      </c>
-      <c r="H18" s="3">
-        <f>AVERAGE(H15:H17)</f>
-        <v>4</v>
-      </c>
-      <c r="I18" s="3">
-        <f>AVERAGE(I15:I17)</f>
-        <v>2</v>
-      </c>
-      <c r="J18" s="3">
-        <f>AVERAGE(J15:J17)</f>
-        <v>2</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="E18" s="4">
+        <f t="shared" ref="E18:J18" si="2">AVERAGE(E15:E17)</f>
+        <v>3</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="I18" s="4">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J18" s="4">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="K18" s="4">
         <f>SUM(E18:J18)</f>
         <v>17</v>
       </c>
@@ -1130,40 +1131,68 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E23" s="3">
-        <f>AVERAGE(E20:E22)</f>
+      <c r="E23" s="4">
+        <f t="shared" ref="E23:J23" si="3">AVERAGE(E20:E22)</f>
         <v>4.666666666666667</v>
       </c>
-      <c r="F23" s="3">
-        <f>AVERAGE(F20:F22)</f>
+      <c r="F23" s="4">
+        <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="G23" s="3">
-        <f>AVERAGE(G20:G22)</f>
+      <c r="G23" s="4">
+        <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="H23" s="3">
-        <f>AVERAGE(H20:H22)</f>
+      <c r="H23" s="4">
+        <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="I23" s="3">
-        <f>AVERAGE(I20:I22)</f>
-        <v>3</v>
-      </c>
-      <c r="J23" s="3">
-        <f>AVERAGE(J20:J22)</f>
+      <c r="I23" s="4">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J23" s="4">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="4">
         <f>SUM(E23:J23)</f>
         <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E25" s="4">
+        <f>AVERAGE(E18,E23)</f>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="F25" s="4">
+        <f>AVERAGE(F18,F23)</f>
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="G25" s="4">
+        <f>AVERAGE(G18,G23)</f>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="H25" s="4">
+        <f>AVERAGE(H18,H23)</f>
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="I25" s="4">
+        <f>AVERAGE(I18,I23)</f>
+        <v>2.5</v>
+      </c>
+      <c r="J25" s="4">
+        <f>AVERAGE(J18,J23)</f>
+        <v>1.5</v>
+      </c>
+      <c r="K25" s="4">
+        <f>AVERAGE(K18,K23)</f>
+        <v>19.5</v>
+      </c>
       <c r="L25" t="s">
         <v>15</v>
       </c>
-      <c r="M25" s="3">
+      <c r="M25" s="4">
         <f>(K18+K23)/2</f>
         <v>19.5</v>
       </c>
@@ -1218,13 +1247,13 @@
         <v>13</v>
       </c>
       <c r="E28" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="2">
         <v>4</v>
@@ -1233,10 +1262,10 @@
         <v>3</v>
       </c>
       <c r="J28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1256,22 +1285,22 @@
         <v>3</v>
       </c>
       <c r="F29" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="2">
         <v>2</v>
       </c>
       <c r="K29" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1288,13 +1317,13 @@
         <v>13</v>
       </c>
       <c r="E30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="2">
         <v>4</v>
@@ -1303,40 +1332,40 @@
         <v>3</v>
       </c>
       <c r="J30" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E31" s="3">
-        <f>AVERAGE(E28:E30)</f>
-        <v>3</v>
-      </c>
-      <c r="F31" s="3">
-        <f>AVERAGE(F28:F30)</f>
-        <v>3</v>
-      </c>
-      <c r="G31" s="3">
-        <f>AVERAGE(G28:G30)</f>
-        <v>3</v>
-      </c>
-      <c r="H31" s="3">
-        <f>AVERAGE(H28:H30)</f>
-        <v>4</v>
-      </c>
-      <c r="I31" s="3">
-        <f>AVERAGE(I28:I30)</f>
+      <c r="E31" s="4">
+        <f t="shared" ref="E31:J31" si="4">AVERAGE(E28:E30)</f>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="F31" s="4">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="G31" s="4">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H31" s="4">
+        <f t="shared" si="4"/>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="I31" s="4">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J31" s="4">
+        <f t="shared" si="4"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="J31" s="3">
-        <f>AVERAGE(J28:J30)</f>
-        <v>2</v>
-      </c>
-      <c r="K31" s="3">
+      <c r="K31" s="4">
         <f>SUM(E31:J31)</f>
-        <v>17.666666666666664</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1446,48 +1475,77 @@
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E36" s="3">
-        <f>AVERAGE(E33:E35)</f>
-        <v>5</v>
-      </c>
-      <c r="F36" s="3">
-        <f>AVERAGE(F33:F35)</f>
-        <v>5</v>
-      </c>
-      <c r="G36" s="3">
-        <f>AVERAGE(G33:G35)</f>
-        <v>5</v>
-      </c>
-      <c r="H36" s="3">
-        <f>AVERAGE(H33:H35)</f>
-        <v>5</v>
-      </c>
-      <c r="I36" s="3">
-        <f>AVERAGE(I33:I35)</f>
+      <c r="E36" s="4">
+        <f t="shared" ref="E36:J36" si="5">AVERAGE(E33:E35)</f>
+        <v>5</v>
+      </c>
+      <c r="F36" s="4">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="G36" s="4">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="H36" s="4">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="I36" s="4">
+        <f t="shared" si="5"/>
         <v>3.3333333333333335</v>
       </c>
-      <c r="J36" s="3">
-        <f>AVERAGE(J33:J35)</f>
+      <c r="J36" s="4">
+        <f t="shared" si="5"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="K36" s="3">
+      <c r="K36" s="4">
         <f>SUM(E36:J36)</f>
         <v>24.666666666666664</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O37" s="3">
-        <f>M38-M25</f>
-        <v>1.6666666666666643</v>
-      </c>
+      <c r="O37" s="3"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E38" s="4">
+        <f>AVERAGE(E31,E36)</f>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="F38" s="4">
+        <f>AVERAGE(F31,F36)</f>
+        <v>4.5</v>
+      </c>
+      <c r="G38" s="4">
+        <f>AVERAGE(G31,G36)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H38" s="4">
+        <f>AVERAGE(H31,H36)</f>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="I38" s="4">
+        <f>AVERAGE(I31,I36)</f>
+        <v>3.166666666666667</v>
+      </c>
+      <c r="J38" s="4">
+        <f>AVERAGE(J31,J36)</f>
+        <v>2</v>
+      </c>
+      <c r="K38" s="4">
+        <f>AVERAGE(K31,K36)</f>
+        <v>22.833333333333332</v>
+      </c>
       <c r="L38" t="s">
         <v>15</v>
       </c>
-      <c r="M38" s="3">
+      <c r="M38" s="4">
         <f>(K31+K36)/2</f>
-        <v>21.166666666666664</v>
+        <v>22.833333333333332</v>
+      </c>
+      <c r="O38" s="4">
+        <f>M38-M25</f>
+        <v>3.3333333333333321</v>
       </c>
     </row>
   </sheetData>
@@ -1497,7 +1555,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CBA29D7-7EBA-48EB-937E-15B7BE5A8B53}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -1652,31 +1710,31 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E5" s="3">
-        <f>AVERAGE(E2:E4)</f>
-        <v>4</v>
-      </c>
-      <c r="F5" s="3">
-        <f>AVERAGE(F2:F4)</f>
-        <v>3</v>
-      </c>
-      <c r="G5" s="3">
-        <f>AVERAGE(G2:G4)</f>
-        <v>3</v>
-      </c>
-      <c r="H5" s="3">
-        <f>AVERAGE(H2:H4)</f>
-        <v>4</v>
-      </c>
-      <c r="I5" s="3">
-        <f>AVERAGE(I2:I4)</f>
-        <v>2</v>
-      </c>
-      <c r="J5" s="3">
-        <f>AVERAGE(J2:J4)</f>
+      <c r="E5" s="4">
+        <f t="shared" ref="E5:J5" si="0">AVERAGE(E2:E4)</f>
+        <v>4</v>
+      </c>
+      <c r="F5" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H5" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I5" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="J5" s="4">
+        <f t="shared" si="0"/>
         <v>2.3333333333333335</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="4">
         <f>SUM(E5:J5)</f>
         <v>18.333333333333332</v>
       </c>
@@ -1788,40 +1846,68 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E10" s="3">
-        <f>AVERAGE(E7:E9)</f>
-        <v>4</v>
-      </c>
-      <c r="F10" s="3">
-        <f>AVERAGE(F7:F9)</f>
+      <c r="E10" s="4">
+        <f t="shared" ref="E10:J10" si="1">AVERAGE(E7:E9)</f>
+        <v>4</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="1"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="G10" s="3">
-        <f>AVERAGE(G7:G9)</f>
+      <c r="G10" s="4">
+        <f t="shared" si="1"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="H10" s="3">
-        <f>AVERAGE(H7:H9)</f>
+      <c r="H10" s="4">
+        <f t="shared" si="1"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="I10" s="3">
-        <f>AVERAGE(I7:I9)</f>
+      <c r="I10" s="4">
+        <f t="shared" si="1"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="J10" s="3">
-        <f>AVERAGE(J7:J9)</f>
+      <c r="J10" s="4">
+        <f t="shared" si="1"/>
         <v>2.3333333333333335</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="4">
         <f>SUM(E10:J10)</f>
         <v>21.333333333333332</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E12" s="4">
+        <f>AVERAGE(E5,E10)</f>
+        <v>4</v>
+      </c>
+      <c r="F12" s="4">
+        <f>AVERAGE(F5,F10)</f>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="G12" s="4">
+        <f>AVERAGE(G5,G10)</f>
+        <v>3.333333333333333</v>
+      </c>
+      <c r="H12" s="4">
+        <f>AVERAGE(H5,H10)</f>
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="I12" s="4">
+        <f>AVERAGE(I5,I10)</f>
+        <v>2.333333333333333</v>
+      </c>
+      <c r="J12" s="4">
+        <f>AVERAGE(J5,J10)</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="K12" s="4">
+        <f>AVERAGE(K5,K10)</f>
+        <v>19.833333333333332</v>
+      </c>
       <c r="L12" t="s">
         <v>15</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="4">
         <f>(K5+K10)/2</f>
         <v>19.833333333333332</v>
       </c>
@@ -1932,7 +2018,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -1967,38 +2053,38 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E18" s="3">
-        <f>AVERAGE(E15:E17)</f>
-        <v>4</v>
-      </c>
-      <c r="F18" s="3">
-        <f>AVERAGE(F15:F17)</f>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E18" s="4">
+        <f t="shared" ref="E18:J18" si="2">AVERAGE(E15:E17)</f>
+        <v>4</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="2"/>
         <v>3.3333333333333335</v>
       </c>
-      <c r="G18" s="3">
-        <f>AVERAGE(G15:G17)</f>
-        <v>4</v>
-      </c>
-      <c r="H18" s="3">
-        <f>AVERAGE(H15:H17)</f>
-        <v>4</v>
-      </c>
-      <c r="I18" s="3">
-        <f>AVERAGE(I15:I17)</f>
+      <c r="G18" s="4">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="I18" s="4">
+        <f t="shared" si="2"/>
         <v>2.3333333333333335</v>
       </c>
-      <c r="J18" s="3">
-        <f>AVERAGE(J15:J17)</f>
+      <c r="J18" s="4">
+        <f t="shared" si="2"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="4">
         <f>SUM(E18:J18)</f>
         <v>20.333333333333336</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
@@ -2033,7 +2119,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
@@ -2068,7 +2154,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
@@ -2103,46 +2189,78 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E23" s="3">
-        <f>AVERAGE(E20:E22)</f>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E23" s="4">
+        <f t="shared" ref="E23:J23" si="3">AVERAGE(E20:E22)</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="F23" s="3">
-        <f>AVERAGE(F20:F22)</f>
+      <c r="F23" s="4">
+        <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="G23" s="3">
-        <f>AVERAGE(G20:G22)</f>
-        <v>5</v>
-      </c>
-      <c r="H23" s="3">
-        <f>AVERAGE(H20:H22)</f>
+      <c r="G23" s="4">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="H23" s="4">
+        <f t="shared" si="3"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="I23" s="3">
-        <f>AVERAGE(I20:I22)</f>
-        <v>3</v>
-      </c>
-      <c r="J23" s="3">
-        <f>AVERAGE(J20:J22)</f>
+      <c r="I23" s="4">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J23" s="4">
+        <f t="shared" si="3"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="4">
         <f>SUM(E23:J23)</f>
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E25" s="4">
+        <f>AVERAGE(E18,E23)</f>
+        <v>3.833333333333333</v>
+      </c>
+      <c r="F25" s="4">
+        <f>AVERAGE(F18,F23)</f>
+        <v>3.833333333333333</v>
+      </c>
+      <c r="G25" s="4">
+        <f>AVERAGE(G18,G23)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H25" s="4">
+        <f>AVERAGE(H18,H23)</f>
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="I25" s="4">
+        <f>AVERAGE(I18,I23)</f>
+        <v>2.666666666666667</v>
+      </c>
+      <c r="J25" s="4">
+        <f>AVERAGE(J18,J23)</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="K25" s="4">
+        <f>AVERAGE(K18,K23)</f>
+        <v>21.666666666666668</v>
+      </c>
       <c r="L25" t="s">
         <v>15</v>
       </c>
-      <c r="M25" s="3">
+      <c r="M25" s="4">
         <f>(K18+K23)/2</f>
         <v>21.666666666666668</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O25" s="4">
+        <f>M25-M12</f>
+        <v>1.8333333333333357</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="M27" s="3"/>
     </row>
   </sheetData>
@@ -2151,6 +2269,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="60ce1e1a-3fa5-4136-b143-4a66d0d8b25a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EF65F10B7F80594B8A9F81F66742701E" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="aefb3758fc152d4724e46b6324be38fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="60ce1e1a-3fa5-4136-b143-4a66d0d8b25a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d044827567d57a65d7f9efb37eed34d" ns3:_="">
     <xsd:import namespace="60ce1e1a-3fa5-4136-b143-4a66d0d8b25a"/>
@@ -2318,24 +2453,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4517D7E1-4D7A-43BC-9356-F7682B03B598}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="60ce1e1a-3fa5-4136-b143-4a66d0d8b25a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="60ce1e1a-3fa5-4136-b143-4a66d0d8b25a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0B14447-2C2D-44B5-8BBC-E83878319151}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34A2B1B8-204C-4E0F-A564-96ED27206D38}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2351,28 +2493,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0B14447-2C2D-44B5-8BBC-E83878319151}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4517D7E1-4D7A-43BC-9356-F7682B03B598}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="60ce1e1a-3fa5-4136-b143-4a66d0d8b25a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>